--- a/data/05_robustness.xlsx
+++ b/data/05_robustness.xlsx
@@ -515,7 +515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -555,7 +555,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -579,7 +579,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4.3 positions</t>
+          <t>3.9 positions</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Rank range: 28 positions</t>
+          <t>Rank range: 30 positions</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Rank range: 25 positions</t>
+          <t>Rank range: 26 positions</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Mauritania</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -690,12 +690,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Burundi</t>
+          <t>Mauritania</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Rank range: 15 positions</t>
+          <t>Rank range: 16 positions</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -707,7 +707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>Malawi</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -716,6 +716,23 @@
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Sensitive</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Burundi</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Rank range: 13 positions</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>Sensitive</t>
         </is>
@@ -788,16 +805,16 @@
         <v>1</v>
       </c>
       <c r="C2" s="8" t="n">
-        <v>0.9486</v>
+        <v>0.9488</v>
       </c>
       <c r="D2" s="8" t="n">
-        <v>0.9694</v>
+        <v>0.97</v>
       </c>
       <c r="E2" s="8" t="n">
-        <v>0.9889</v>
+        <v>0.9927</v>
       </c>
       <c r="F2" s="8" t="n">
-        <v>0.9651999999999999</v>
+        <v>0.9675</v>
       </c>
     </row>
     <row r="3">
@@ -807,19 +824,19 @@
         </is>
       </c>
       <c r="B3" s="8" t="n">
-        <v>0.9486</v>
+        <v>0.9488</v>
       </c>
       <c r="C3" s="7" t="n">
         <v>1</v>
       </c>
       <c r="D3" s="8" t="n">
-        <v>0.9388</v>
+        <v>0.9376</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>0.9328</v>
+        <v>0.9325</v>
       </c>
       <c r="F3" s="8" t="n">
-        <v>0.9063</v>
+        <v>0.8995</v>
       </c>
     </row>
     <row r="4">
@@ -829,16 +846,16 @@
         </is>
       </c>
       <c r="B4" s="8" t="n">
-        <v>0.9694</v>
+        <v>0.97</v>
       </c>
       <c r="C4" s="8" t="n">
-        <v>0.9388</v>
+        <v>0.9376</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>1</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>0.9540999999999999</v>
+        <v>0.9597</v>
       </c>
       <c r="F4" s="8" t="n">
         <v>0.8988</v>
@@ -851,19 +868,19 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>0.9889</v>
+        <v>0.9927</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>0.9328</v>
+        <v>0.9325</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>0.9540999999999999</v>
+        <v>0.9597</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>0.9655</v>
+        <v>0.9676</v>
       </c>
     </row>
     <row r="6">
@@ -873,16 +890,16 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>0.9651999999999999</v>
+        <v>0.9675</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>0.9063</v>
+        <v>0.8995</v>
       </c>
       <c r="D6" s="8" t="n">
         <v>0.8988</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>0.9655</v>
+        <v>0.9676</v>
       </c>
       <c r="F6" s="7" t="n">
         <v>1</v>
@@ -1069,28 +1086,28 @@
       </c>
       <c r="D2" s="10" t="inlineStr"/>
       <c r="E2" s="11" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G2" s="11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H2" s="11" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I2" s="11" t="n">
         <v>49</v>
       </c>
       <c r="J2" s="11" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K2" s="11" t="n">
         <v>49</v>
       </c>
       <c r="L2" s="11" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="M2" s="12" t="inlineStr">
         <is>
@@ -1116,28 +1133,28 @@
       </c>
       <c r="D3" s="10" t="inlineStr"/>
       <c r="E3" s="11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F3" s="11" t="n">
         <v>6</v>
       </c>
       <c r="G3" s="11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H3" s="11" t="n">
         <v>14</v>
       </c>
       <c r="I3" s="11" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J3" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K3" s="11" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L3" s="11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M3" s="12" t="inlineStr">
         <is>
@@ -1163,25 +1180,25 @@
       </c>
       <c r="D4" s="10" t="inlineStr"/>
       <c r="E4" s="11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G4" s="11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H4" s="11" t="n">
         <v>13</v>
       </c>
       <c r="I4" s="11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J4" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K4" s="11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L4" s="11" t="n">
         <v>19</v>
@@ -1195,40 +1212,40 @@
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>MRT</t>
+          <t>TZA</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>Mauritania</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D5" s="10" t="inlineStr"/>
       <c r="E5" s="11" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H5" s="11" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="J5" s="11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L5" s="11" t="n">
         <v>16</v>
@@ -1242,43 +1259,43 @@
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>BDI</t>
+          <t>MRT</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>Burundi</t>
+          <t>Mauritania</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr"/>
       <c r="E6" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="G6" s="11" t="n">
         <v>34</v>
       </c>
-      <c r="F6" s="11" t="n">
-        <v>45</v>
-      </c>
-      <c r="G6" s="11" t="n">
+      <c r="H6" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="H6" s="11" t="n">
-        <v>35</v>
-      </c>
       <c r="I6" s="11" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="J6" s="11" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="K6" s="11" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="L6" s="11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M6" s="12" t="inlineStr">
         <is>
@@ -1289,12 +1306,12 @@
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>TZA</t>
+          <t>MWI</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>Malawi</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
@@ -1304,25 +1321,25 @@
       </c>
       <c r="D7" s="10" t="inlineStr"/>
       <c r="E7" s="11" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="H7" s="11" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J7" s="11" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="L7" s="11" t="n">
         <v>13</v>
@@ -1336,12 +1353,12 @@
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>MWI</t>
+          <t>BDI</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>Malawi</t>
+          <t>Burundi</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
@@ -1351,75 +1368,75 @@
       </c>
       <c r="D8" s="10" t="inlineStr"/>
       <c r="E8" s="11" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="H8" s="11" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="J8" s="11" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="K8" s="11" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="L8" s="11" t="n">
-        <v>12</v>
-      </c>
-      <c r="M8" s="13" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>13</v>
+      </c>
+      <c r="M8" s="12" t="inlineStr">
+        <is>
+          <t>Sensitive</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>AGO</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr"/>
       <c r="E9" s="11" t="n">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="G9" s="11" t="n">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="H9" s="11" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="J9" s="11" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="L9" s="11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M9" s="13" t="inlineStr">
         <is>
@@ -1430,43 +1447,43 @@
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>COG</t>
+          <t>GIN</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Republic of Congo</t>
+          <t>Guinea</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr"/>
       <c r="E10" s="11" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="I10" s="11" t="n">
         <v>34</v>
       </c>
       <c r="J10" s="11" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K10" s="11" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="L10" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M10" s="13" t="inlineStr">
         <is>
@@ -1477,12 +1494,12 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>GAB</t>
+          <t>COG</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>Gabon</t>
+          <t>Republic of Congo</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
@@ -1492,28 +1509,28 @@
       </c>
       <c r="D11" s="10" t="inlineStr"/>
       <c r="E11" s="11" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="G11" s="11" t="n">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="H11" s="11" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="J11" s="11" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="L11" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M11" s="13" t="inlineStr">
         <is>
@@ -1524,43 +1541,43 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>KEN</t>
+          <t>LSO</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Lesotho</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr"/>
       <c r="E12" s="11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="H12" s="11" t="n">
         <v>17</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="J12" s="11" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K12" s="11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L12" s="11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M12" s="13" t="inlineStr">
         <is>
@@ -1571,43 +1588,43 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>GAB</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>Gabon</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr"/>
       <c r="E13" s="11" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F13" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="G13" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="H13" s="11" t="n">
         <v>29</v>
       </c>
-      <c r="G13" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="H13" s="11" t="n">
-        <v>22</v>
-      </c>
       <c r="I13" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="J13" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="J13" s="11" t="n">
-        <v>19</v>
-      </c>
       <c r="K13" s="11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L13" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M13" s="13" t="inlineStr">
         <is>
@@ -1618,43 +1635,43 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>LSO</t>
+          <t>BFA</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>Burkina Faso</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr"/>
       <c r="E14" s="11" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="J14" s="11" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="K14" s="11" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="L14" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M14" s="13" t="inlineStr">
         <is>
@@ -1665,12 +1682,12 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>GMB</t>
+          <t>GNB</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>The Gambia</t>
+          <t>Guinea-Bissau</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
@@ -1680,28 +1697,28 @@
       </c>
       <c r="D15" s="10" t="inlineStr"/>
       <c r="E15" s="11" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="G15" s="11" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="H15" s="11" t="n">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="J15" s="11" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="L15" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M15" s="13" t="inlineStr">
         <is>
@@ -1712,43 +1729,43 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>GIN</t>
+          <t>AGO</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Guinea</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr"/>
       <c r="E16" s="11" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="J16" s="11" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="L16" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M16" s="13" t="inlineStr">
         <is>
@@ -1759,40 +1776,40 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>NAM</t>
+          <t>SLE</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Sierra Leone</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr"/>
       <c r="E17" s="11" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="G17" s="11" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="H17" s="11" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="J17" s="11" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="L17" s="11" t="n">
         <v>8</v>
@@ -1806,12 +1823,12 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>BFA</t>
+          <t>GMB</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Burkina Faso</t>
+          <t>The Gambia</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
@@ -1821,28 +1838,28 @@
       </c>
       <c r="D18" s="10" t="inlineStr"/>
       <c r="E18" s="11" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="H18" s="11" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="I18" s="11" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="J18" s="11" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="K18" s="11" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="L18" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M18" s="13" t="inlineStr">
         <is>
@@ -1853,12 +1870,12 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>ZWE</t>
+          <t>DJI</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Djibouti</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
@@ -1868,28 +1885,28 @@
       </c>
       <c r="D19" s="10" t="inlineStr"/>
       <c r="E19" s="11" t="n">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="H19" s="11" t="n">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="I19" s="11" t="n">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="J19" s="11" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="L19" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M19" s="13" t="inlineStr">
         <is>
@@ -1900,43 +1917,43 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>SLE</t>
+          <t>CMR</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Sierra Leone</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr"/>
       <c r="E20" s="11" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="H20" s="11" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="I20" s="11" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="J20" s="11" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="K20" s="11" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="L20" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M20" s="13" t="inlineStr">
         <is>
@@ -1947,40 +1964,40 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>GNB</t>
+          <t>NAM</t>
         </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>Guinea-Bissau</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr"/>
       <c r="E21" s="11" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="H21" s="11" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="I21" s="11" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="J21" s="11" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="L21" s="11" t="n">
         <v>7</v>
@@ -1994,40 +2011,44 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>MOZ</t>
+          <t>COM</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Comoros</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>East</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr"/>
+          <t>Islands</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="E22" s="11" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="H22" s="11" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="I22" s="11" t="n">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="J22" s="11" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="K22" s="11" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="L22" s="11" t="n">
         <v>7</v>
@@ -2041,40 +2062,40 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>GHA</t>
+          <t>ZMB</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr"/>
       <c r="E23" s="11" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="H23" s="11" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="J23" s="11" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="L23" s="11" t="n">
         <v>6</v>
@@ -2088,40 +2109,40 @@
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>SWZ</t>
+          <t>ZWE</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr"/>
       <c r="E24" s="11" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="H24" s="11" t="n">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="J24" s="11" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="K24" s="11" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="L24" s="11" t="n">
         <v>6</v>
@@ -2135,40 +2156,40 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>CMR</t>
+          <t>GHA</t>
         </is>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr"/>
       <c r="E25" s="11" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="H25" s="11" t="n">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="J25" s="11" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="L25" s="11" t="n">
         <v>6</v>
@@ -2182,12 +2203,12 @@
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>DJI</t>
+          <t>MOZ</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>Djibouti</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
@@ -2197,25 +2218,25 @@
       </c>
       <c r="D26" s="10" t="inlineStr"/>
       <c r="E26" s="11" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H26" s="11" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="J26" s="11" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="K26" s="11" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="L26" s="11" t="n">
         <v>6</v>
@@ -2229,134 +2250,134 @@
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>NER</t>
         </is>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>Niger</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr"/>
       <c r="E27" s="11" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G27" s="11" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="H27" s="11" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J27" s="11" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="L27" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="M27" s="14" t="inlineStr">
-        <is>
-          <t>Stable</t>
+        <v>6</v>
+      </c>
+      <c r="M27" s="13" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>SEN</t>
+          <t>TUN</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr"/>
       <c r="E28" s="11" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F28" s="11" t="n">
         <v>8</v>
       </c>
       <c r="G28" s="11" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H28" s="11" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I28" s="11" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J28" s="11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K28" s="11" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L28" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="M28" s="14" t="inlineStr">
-        <is>
-          <t>Stable</t>
+        <v>6</v>
+      </c>
+      <c r="M28" s="13" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>NER</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>Niger</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr"/>
       <c r="E29" s="11" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G29" s="11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="H29" s="11" t="n">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="J29" s="11" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="K29" s="11" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="L29" s="11" t="n">
         <v>5</v>
@@ -2370,40 +2391,40 @@
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>CIV</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>Democratic Rep. Congo</t>
+          <t>Cote d'Ivoire</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr"/>
       <c r="E30" s="11" t="n">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="G30" s="11" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H30" s="11" t="n">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="I30" s="11" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="J30" s="11" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="K30" s="11" t="n">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="L30" s="11" t="n">
         <v>5</v>
@@ -2417,12 +2438,12 @@
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>LBR</t>
+          <t>BEN</t>
         </is>
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>Liberia</t>
+          <t>Benin</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
@@ -2432,25 +2453,25 @@
       </c>
       <c r="D31" s="10" t="inlineStr"/>
       <c r="E31" s="11" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="G31" s="11" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="H31" s="11" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="J31" s="11" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="L31" s="11" t="n">
         <v>5</v>
@@ -2464,34 +2485,34 @@
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>TUN</t>
+          <t>RWA</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Rwanda</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D32" s="10" t="inlineStr"/>
       <c r="E32" s="11" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G32" s="11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H32" s="11" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I32" s="11" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J32" s="11" t="n">
         <v>9</v>
@@ -2511,12 +2532,12 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>ZMB</t>
+          <t>KEN</t>
         </is>
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
@@ -2526,25 +2547,25 @@
       </c>
       <c r="D33" s="10" t="inlineStr"/>
       <c r="E33" s="11" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G33" s="11" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H33" s="11" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J33" s="11" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="L33" s="11" t="n">
         <v>5</v>
@@ -2558,43 +2579,43 @@
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>BEN</t>
+          <t>SWZ</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>Benin</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D34" s="10" t="inlineStr"/>
       <c r="E34" s="11" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="G34" s="11" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="H34" s="11" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I34" s="11" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J34" s="11" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="K34" s="11" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="L34" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M34" s="14" t="inlineStr">
         <is>
@@ -2605,12 +2626,12 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>CIV</t>
+          <t>TGO</t>
         </is>
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>Cote d'Ivoire</t>
+          <t>Togo</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
@@ -2620,28 +2641,28 @@
       </c>
       <c r="D35" s="10" t="inlineStr"/>
       <c r="E35" s="11" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G35" s="11" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="H35" s="11" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I35" s="11" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="J35" s="11" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="L35" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M35" s="14" t="inlineStr">
         <is>
@@ -2652,40 +2673,44 @@
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>BWA</t>
+          <t>STP</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Sao Tome &amp; Principe</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="D36" s="10" t="inlineStr"/>
+          <t>Islands</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="E36" s="11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="G36" s="11" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="H36" s="11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I36" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J36" s="11" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K36" s="11" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="L36" s="11" t="n">
         <v>4</v>
@@ -2699,44 +2724,40 @@
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>STP</t>
+          <t>BWA</t>
         </is>
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>Sao Tome &amp; Principe</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>Islands</t>
-        </is>
-      </c>
-      <c r="D37" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr"/>
       <c r="E37" s="11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G37" s="11" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="H37" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J37" s="11" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L37" s="11" t="n">
         <v>4</v>
@@ -2765,25 +2786,25 @@
       </c>
       <c r="D38" s="10" t="inlineStr"/>
       <c r="E38" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="F38" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="G38" s="11" t="n">
         <v>14</v>
-      </c>
-      <c r="F38" s="11" t="n">
-        <v>12</v>
-      </c>
-      <c r="G38" s="11" t="n">
-        <v>15</v>
       </c>
       <c r="H38" s="11" t="n">
         <v>11</v>
       </c>
       <c r="I38" s="11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J38" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K38" s="11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L38" s="11" t="n">
         <v>4</v>
@@ -2797,40 +2818,40 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>RWA</t>
+          <t>SEN</t>
         </is>
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr"/>
       <c r="E39" s="11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G39" s="11" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H39" s="11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J39" s="11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="L39" s="11" t="n">
         <v>4</v>
@@ -2844,44 +2865,40 @@
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>MDG</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>Madagascar</t>
+          <t>Democratic Rep. Congo</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>Islands</t>
-        </is>
-      </c>
-      <c r="D40" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>Central</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="inlineStr"/>
       <c r="E40" s="11" t="n">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="G40" s="11" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="H40" s="11" t="n">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="I40" s="11" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="J40" s="11" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="K40" s="11" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="L40" s="11" t="n">
         <v>4</v>
@@ -2895,12 +2912,12 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>COM</t>
+          <t>MDG</t>
         </is>
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>Comoros</t>
+          <t>Madagascar</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
@@ -2914,25 +2931,25 @@
         </is>
       </c>
       <c r="E41" s="11" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="G41" s="11" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H41" s="11" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I41" s="11" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J41" s="11" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="K41" s="11" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="L41" s="11" t="n">
         <v>4</v>
@@ -2946,12 +2963,12 @@
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>TGO</t>
+          <t>MLI</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>Togo</t>
+          <t>Mali</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
@@ -2961,25 +2978,25 @@
       </c>
       <c r="D42" s="10" t="inlineStr"/>
       <c r="E42" s="11" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="G42" s="11" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="H42" s="11" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="I42" s="11" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="J42" s="11" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="K42" s="11" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="L42" s="11" t="n">
         <v>4</v>
@@ -2993,43 +3010,43 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>NGA</t>
+          <t>GNQ</t>
         </is>
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Equatorial Guinea</t>
         </is>
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="D43" s="10" t="inlineStr"/>
       <c r="E43" s="11" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G43" s="11" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="H43" s="11" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="I43" s="11" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J43" s="11" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="K43" s="11" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="L43" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M43" s="14" t="inlineStr">
         <is>
@@ -3040,43 +3057,43 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>ERI</t>
+          <t>LBR</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>Eritrea</t>
+          <t>Liberia</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D44" s="10" t="inlineStr"/>
       <c r="E44" s="11" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="G44" s="11" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="H44" s="11" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="I44" s="11" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="J44" s="11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="K44" s="11" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L44" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M44" s="14" t="inlineStr">
         <is>
@@ -3087,40 +3104,40 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>GNQ</t>
+          <t>NGA</t>
         </is>
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>Equatorial Guinea</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D45" s="10" t="inlineStr"/>
       <c r="E45" s="11" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G45" s="11" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="H45" s="11" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="I45" s="11" t="n">
+        <v>44</v>
+      </c>
+      <c r="J45" s="11" t="n">
+        <v>43</v>
+      </c>
+      <c r="K45" s="11" t="n">
         <v>46</v>
-      </c>
-      <c r="J45" s="11" t="n">
-        <v>46</v>
-      </c>
-      <c r="K45" s="11" t="n">
-        <v>49</v>
       </c>
       <c r="L45" s="11" t="n">
         <v>3</v>
@@ -3134,40 +3151,40 @@
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>MLI</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>Mali</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D46" s="10" t="inlineStr"/>
       <c r="E46" s="11" t="n">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="G46" s="11" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="H46" s="11" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="I46" s="11" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="J46" s="11" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="K46" s="11" t="n">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="L46" s="11" t="n">
         <v>2</v>
@@ -3181,43 +3198,43 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>SDN</t>
+          <t>ERI</t>
         </is>
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>Sudan</t>
+          <t>Eritrea</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D47" s="10" t="inlineStr"/>
       <c r="E47" s="11" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G47" s="11" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H47" s="11" t="n">
         <v>47</v>
       </c>
       <c r="I47" s="11" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J47" s="11" t="n">
+        <v>46</v>
+      </c>
+      <c r="K47" s="11" t="n">
         <v>47</v>
       </c>
-      <c r="K47" s="11" t="n">
-        <v>49</v>
-      </c>
       <c r="L47" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M47" s="14" t="inlineStr">
         <is>
@@ -3246,10 +3263,10 @@
         <v>51</v>
       </c>
       <c r="F48" s="11" t="n">
+        <v>51</v>
+      </c>
+      <c r="G48" s="11" t="n">
         <v>50</v>
-      </c>
-      <c r="G48" s="11" t="n">
-        <v>52</v>
       </c>
       <c r="H48" s="11" t="n">
         <v>51</v>
@@ -3261,10 +3278,10 @@
         <v>50</v>
       </c>
       <c r="K48" s="11" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L48" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M48" s="14" t="inlineStr">
         <is>
@@ -3275,17 +3292,17 @@
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>CAF</t>
+          <t>SOM</t>
         </is>
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>Central African Republic</t>
+          <t>Somalia</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D49" s="10" t="inlineStr"/>
@@ -3293,25 +3310,25 @@
         <v>52</v>
       </c>
       <c r="F49" s="11" t="n">
+        <v>52</v>
+      </c>
+      <c r="G49" s="11" t="n">
         <v>53</v>
       </c>
-      <c r="G49" s="11" t="n">
-        <v>51</v>
-      </c>
       <c r="H49" s="11" t="n">
+        <v>53</v>
+      </c>
+      <c r="I49" s="11" t="n">
         <v>52</v>
       </c>
-      <c r="I49" s="11" t="n">
-        <v>53</v>
-      </c>
       <c r="J49" s="11" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K49" s="11" t="n">
         <v>53</v>
       </c>
       <c r="L49" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M49" s="14" t="inlineStr">
         <is>
@@ -3322,17 +3339,17 @@
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>SOM</t>
+          <t>CAF</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>Somalia</t>
+          <t>Central African Republic</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="D50" s="10" t="inlineStr"/>
@@ -3340,16 +3357,16 @@
         <v>53</v>
       </c>
       <c r="F50" s="11" t="n">
+        <v>53</v>
+      </c>
+      <c r="G50" s="11" t="n">
         <v>52</v>
       </c>
-      <c r="G50" s="11" t="n">
+      <c r="H50" s="11" t="n">
+        <v>52</v>
+      </c>
+      <c r="I50" s="11" t="n">
         <v>53</v>
-      </c>
-      <c r="H50" s="11" t="n">
-        <v>53</v>
-      </c>
-      <c r="I50" s="11" t="n">
-        <v>52</v>
       </c>
       <c r="J50" s="11" t="n">
         <v>52</v>
@@ -3369,12 +3386,12 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>SDN</t>
         </is>
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Sudan</t>
         </is>
       </c>
       <c r="C51" s="10" t="inlineStr">
@@ -3384,25 +3401,25 @@
       </c>
       <c r="D51" s="10" t="inlineStr"/>
       <c r="E51" s="11" t="n">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="G51" s="11" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="H51" s="11" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="I51" s="11" t="n">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="J51" s="11" t="n">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="K51" s="11" t="n">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="L51" s="11" t="n">
         <v>1</v>
@@ -3680,7 +3697,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.9245</t>
+          <t>0.9394</t>
         </is>
       </c>
     </row>
@@ -3692,7 +3709,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4.3 positions</t>
+          <t>3.9 positions</t>
         </is>
       </c>
     </row>
@@ -3704,7 +3721,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19 positions</t>
+          <t>16 positions</t>
         </is>
       </c>
     </row>
@@ -3864,7 +3881,7 @@
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>Interpretation: Even in the worst case (rho=0.924), the mean rank shift is 4.3 positions. Verdict: Robust.</t>
+          <t>Interpretation: Even in the worst case (rho=0.939), the mean rank shift is 3.9 positions. Verdict: Robust.</t>
         </is>
       </c>
     </row>
@@ -3933,27 +3950,27 @@
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>GIN</t>
+          <t>ERI</t>
         </is>
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>Guinea</t>
+          <t>Eritrea</t>
         </is>
       </c>
       <c r="C2" s="10" t="inlineStr"/>
       <c r="D2" s="11" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="G2" s="13" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>9</v>
+      </c>
+      <c r="G2" s="12" t="inlineStr">
+        <is>
+          <t>Data-sensitive</t>
         </is>
       </c>
     </row>
@@ -3970,40 +3987,40 @@
       </c>
       <c r="C3" s="10" t="inlineStr"/>
       <c r="D3" s="11" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="G3" s="13" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>9</v>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>Data-sensitive</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>AGO</t>
+          <t>LBY</t>
         </is>
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Libya</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr"/>
       <c r="D4" s="11" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G4" s="13" t="inlineStr">
         <is>
@@ -4014,23 +4031,23 @@
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>COG</t>
+          <t>GIN</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>Republic of Congo</t>
+          <t>Guinea</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr"/>
       <c r="D5" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="E5" s="11" t="n">
         <v>39</v>
       </c>
-      <c r="E5" s="11" t="n">
-        <v>33</v>
-      </c>
       <c r="F5" s="11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G5" s="13" t="inlineStr">
         <is>
@@ -4041,23 +4058,23 @@
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>LSO</t>
+          <t>AGO</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr"/>
       <c r="D6" s="11" t="n">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
@@ -4068,23 +4085,23 @@
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>LBR</t>
+          <t>COG</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>Liberia</t>
+          <t>Republic of Congo</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr"/>
       <c r="D7" s="11" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G7" s="13" t="inlineStr">
         <is>
@@ -4095,20 +4112,20 @@
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>LBY</t>
+          <t>LBR</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>Libya</t>
+          <t>Liberia</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr"/>
       <c r="D8" s="11" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="F8" s="11" t="n">
         <v>5</v>
@@ -4122,20 +4139,20 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>GNB</t>
+          <t>TGO</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>Guinea-Bissau</t>
+          <t>Togo</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr"/>
       <c r="D9" s="11" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F9" s="11" t="n">
         <v>4</v>
@@ -4149,20 +4166,20 @@
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>RWA</t>
+          <t>LSO</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>Lesotho</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr"/>
       <c r="D10" s="11" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F10" s="11" t="n">
         <v>4</v>
@@ -4176,20 +4193,20 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>RWA</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Rwanda</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr"/>
       <c r="D11" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F11" s="11" t="n">
         <v>4</v>
@@ -4203,47 +4220,51 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>BEN</t>
+          <t>TZA</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Benin</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr"/>
       <c r="D12" s="11" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="G12" s="14" t="inlineStr">
-        <is>
-          <t>Stable</t>
+        <v>4</v>
+      </c>
+      <c r="G12" s="13" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>BWA</t>
+          <t>COM</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>Botswana</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="inlineStr"/>
+          <t>Comoros</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="D13" s="11" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F13" s="11" t="n">
         <v>3</v>
@@ -4257,20 +4278,20 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>NAM</t>
+          <t>GNB</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Guinea-Bissau</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr"/>
       <c r="D14" s="11" t="n">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="F14" s="11" t="n">
         <v>3</v>
@@ -4284,20 +4305,20 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>CIV</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>Cote d'Ivoire</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr"/>
       <c r="D15" s="11" t="n">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F15" s="11" t="n">
         <v>3</v>
@@ -4311,20 +4332,20 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>TZA</t>
+          <t>NAM</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr"/>
       <c r="D16" s="11" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="F16" s="11" t="n">
         <v>3</v>
@@ -4348,13 +4369,13 @@
       </c>
       <c r="C17" s="10" t="inlineStr"/>
       <c r="D17" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="E17" s="11" t="n">
         <v>22</v>
       </c>
-      <c r="E17" s="11" t="n">
-        <v>25</v>
-      </c>
       <c r="F17" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
@@ -4365,23 +4386,23 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>ZAF</t>
+          <t>KEN</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr"/>
       <c r="D18" s="11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E18" s="11" t="n">
         <v>17</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
@@ -4392,20 +4413,20 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>EGY</t>
+          <t>ZMB</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr"/>
       <c r="D19" s="11" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F19" s="11" t="n">
         <v>2</v>
@@ -4419,20 +4440,20 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>SEN</t>
+          <t>CIV</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Cote d'Ivoire</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr"/>
       <c r="D20" s="11" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F20" s="11" t="n">
         <v>2</v>
@@ -4446,20 +4467,20 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>GNQ</t>
+          <t>MWI</t>
         </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>Equatorial Guinea</t>
+          <t>Malawi</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr"/>
       <c r="D21" s="11" t="n">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="F21" s="11" t="n">
         <v>2</v>
@@ -4473,20 +4494,20 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>MOZ</t>
+          <t>BWA</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr"/>
       <c r="D22" s="11" t="n">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="F22" s="11" t="n">
         <v>2</v>
@@ -4500,20 +4521,20 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>ZWE</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr"/>
       <c r="D23" s="11" t="n">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="F23" s="11" t="n">
         <v>2</v>
@@ -4527,20 +4548,20 @@
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>SDN</t>
+          <t>CMR</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>Sudan</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr"/>
       <c r="D24" s="11" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="F24" s="11" t="n">
         <v>2</v>
@@ -4554,23 +4575,23 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>SDN</t>
         </is>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>Democratic Rep. Congo</t>
+          <t>Sudan</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr"/>
       <c r="D25" s="11" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G25" s="14" t="inlineStr">
         <is>
@@ -4581,12 +4602,12 @@
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>MOZ</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr"/>
@@ -4594,10 +4615,10 @@
         <v>40</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G26" s="14" t="inlineStr">
         <is>
@@ -4608,20 +4629,20 @@
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>TCD</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>Chad</t>
+          <t>Democratic Rep. Congo</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr"/>
       <c r="D27" s="11" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F27" s="11" t="n">
         <v>1</v>
@@ -4635,20 +4656,20 @@
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>SLE</t>
+          <t>CAF</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>Sierra Leone</t>
+          <t>Central African Republic</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr"/>
       <c r="D28" s="11" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="F28" s="11" t="n">
         <v>1</v>
@@ -4662,20 +4683,20 @@
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>DZA</t>
+          <t>SOM</t>
         </is>
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Somalia</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr"/>
       <c r="D29" s="11" t="n">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="F29" s="11" t="n">
         <v>1</v>
@@ -4689,20 +4710,20 @@
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>MWI</t>
+          <t>TCD</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>Malawi</t>
+          <t>Chad</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr"/>
       <c r="D30" s="11" t="n">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="F30" s="11" t="n">
         <v>1</v>
@@ -4716,20 +4737,20 @@
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>ZMB</t>
+          <t>BEN</t>
         </is>
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Benin</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr"/>
       <c r="D31" s="11" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F31" s="11" t="n">
         <v>1</v>
@@ -4743,20 +4764,24 @@
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>GHA</t>
+          <t>CPV</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>Ghana</t>
-        </is>
-      </c>
-      <c r="C32" s="10" t="inlineStr"/>
+          <t>Cabo Verde</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="D32" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F32" s="11" t="n">
         <v>1</v>
@@ -4770,12 +4795,12 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>STP</t>
+          <t>SYC</t>
         </is>
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>Sao Tome &amp; Principe</t>
+          <t>Seychelles</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
@@ -4784,10 +4809,10 @@
         </is>
       </c>
       <c r="D33" s="11" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F33" s="11" t="n">
         <v>1</v>
@@ -4801,20 +4826,20 @@
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>TUN</t>
+          <t>SEN</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr"/>
       <c r="D34" s="11" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F34" s="11" t="n">
         <v>1</v>
@@ -4828,24 +4853,20 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>MDG</t>
+          <t>TUN</t>
         </is>
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>Madagascar</t>
-        </is>
-      </c>
-      <c r="C35" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr"/>
       <c r="D35" s="11" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F35" s="11" t="n">
         <v>1</v>
@@ -4859,20 +4880,20 @@
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>BDI</t>
+          <t>SWZ</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>Burundi</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr"/>
       <c r="D36" s="11" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="F36" s="11" t="n">
         <v>1</v>
@@ -4886,20 +4907,20 @@
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>MRT</t>
+          <t>BFA</t>
         </is>
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>Mauritania</t>
+          <t>Burkina Faso</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr"/>
       <c r="D37" s="11" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F37" s="11" t="n">
         <v>1</v>
@@ -4913,20 +4934,24 @@
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>TGO</t>
+          <t>STP</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>Togo</t>
-        </is>
-      </c>
-      <c r="C38" s="10" t="inlineStr"/>
+          <t>Sao Tome &amp; Principe</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="D38" s="11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F38" s="11" t="n">
         <v>1</v>
@@ -4940,20 +4965,20 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>SWZ</t>
+          <t>BDI</t>
         </is>
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>Burundi</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr"/>
       <c r="D39" s="11" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F39" s="11" t="n">
         <v>1</v>
@@ -4967,20 +4992,20 @@
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>NGA</t>
+          <t>MLI</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Mali</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr"/>
       <c r="D40" s="11" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F40" s="11" t="n">
         <v>1</v>
@@ -4994,23 +5019,23 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>DJI</t>
+          <t>EGY</t>
         </is>
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>Djibouti</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr"/>
       <c r="D41" s="11" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
@@ -5031,10 +5056,10 @@
       </c>
       <c r="C42" s="10" t="inlineStr"/>
       <c r="D42" s="11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F42" s="11" t="n">
         <v>0</v>
@@ -5048,24 +5073,20 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>CPV</t>
+          <t>DZA</t>
         </is>
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>Cabo Verde</t>
-        </is>
-      </c>
-      <c r="C43" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>Algeria</t>
+        </is>
+      </c>
+      <c r="C43" s="10" t="inlineStr"/>
       <c r="D43" s="11" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="F43" s="11" t="n">
         <v>0</v>
@@ -5079,24 +5100,20 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>MUS</t>
+          <t>GHA</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>Mauritius</t>
-        </is>
-      </c>
-      <c r="C44" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="C44" s="10" t="inlineStr"/>
       <c r="D44" s="11" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F44" s="11" t="n">
         <v>0</v>
@@ -5110,20 +5127,24 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>KEN</t>
+          <t>MUS</t>
         </is>
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>Kenya</t>
-        </is>
-      </c>
-      <c r="C45" s="10" t="inlineStr"/>
+          <t>Mauritius</t>
+        </is>
+      </c>
+      <c r="C45" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="D45" s="11" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="F45" s="11" t="n">
         <v>0</v>
@@ -5137,24 +5158,20 @@
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>SYC</t>
+          <t>ZAF</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>Seychelles</t>
-        </is>
-      </c>
-      <c r="C46" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="C46" s="10" t="inlineStr"/>
       <c r="D46" s="11" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F46" s="11" t="n">
         <v>0</v>
@@ -5168,24 +5185,20 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>COM</t>
+          <t>SLE</t>
         </is>
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>Comoros</t>
-        </is>
-      </c>
-      <c r="C47" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>Sierra Leone</t>
+        </is>
+      </c>
+      <c r="C47" s="10" t="inlineStr"/>
       <c r="D47" s="11" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F47" s="11" t="n">
         <v>0</v>
@@ -5199,20 +5212,24 @@
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>CMR</t>
+          <t>MDG</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>Cameroon</t>
-        </is>
-      </c>
-      <c r="C48" s="10" t="inlineStr"/>
+          <t>Madagascar</t>
+        </is>
+      </c>
+      <c r="C48" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="D48" s="11" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F48" s="11" t="n">
         <v>0</v>
@@ -5226,20 +5243,20 @@
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>BFA</t>
+          <t>DJI</t>
         </is>
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>Burkina Faso</t>
+          <t>Djibouti</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr"/>
       <c r="D49" s="11" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F49" s="11" t="n">
         <v>0</v>
@@ -5253,20 +5270,20 @@
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>NER</t>
+          <t>MRT</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>Niger</t>
+          <t>Mauritania</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr"/>
       <c r="D50" s="11" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="F50" s="11" t="n">
         <v>0</v>
@@ -5280,20 +5297,20 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>MLI</t>
+          <t>ZWE</t>
         </is>
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>Mali</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="C51" s="10" t="inlineStr"/>
       <c r="D51" s="11" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F51" s="11" t="n">
         <v>0</v>
@@ -5307,20 +5324,20 @@
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>ERI</t>
+          <t>NER</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t>Eritrea</t>
+          <t>Niger</t>
         </is>
       </c>
       <c r="C52" s="10" t="inlineStr"/>
       <c r="D52" s="11" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E52" s="11" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F52" s="11" t="n">
         <v>0</v>
@@ -5334,20 +5351,20 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>CAF</t>
+          <t>NGA</t>
         </is>
       </c>
       <c r="B53" s="10" t="inlineStr">
         <is>
-          <t>Central African Republic</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="C53" s="10" t="inlineStr"/>
       <c r="D53" s="11" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="E53" s="11" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="F53" s="11" t="n">
         <v>0</v>
@@ -5361,20 +5378,20 @@
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>SOM</t>
+          <t>GNQ</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t>Somalia</t>
+          <t>Equatorial Guinea</t>
         </is>
       </c>
       <c r="C54" s="10" t="inlineStr"/>
       <c r="D54" s="11" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E54" s="11" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="F54" s="11" t="n">
         <v>0</v>
@@ -5494,52 +5511,52 @@
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>KEN</t>
+          <t>LBY</t>
         </is>
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Libya</t>
         </is>
       </c>
       <c r="C3" s="11" t="n">
         <v>24</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>LBY</t>
+          <t>COM</t>
         </is>
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>Libya</t>
+          <t>Comoros</t>
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E4" s="11" t="n">
         <v>3</v>
@@ -5557,10 +5574,10 @@
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E5" s="11" t="n">
         <v>3</v>
@@ -5590,40 +5607,40 @@
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>NAM</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>Democratic Rep. Congo</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>GAB</t>
+          <t>MDG</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>Gabon</t>
+          <t>Madagascar</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E8" s="11" t="n">
         <v>2</v>
@@ -5632,19 +5649,19 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>GNB</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>Guinea-Bissau</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E9" s="11" t="n">
         <v>2</v>
@@ -5653,19 +5670,19 @@
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>MDG</t>
+          <t>GNB</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Madagascar</t>
+          <t>Guinea-Bissau</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="E10" s="11" t="n">
         <v>2</v>
@@ -5674,19 +5691,19 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>GHA</t>
+          <t>EGY</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
         <v>7</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E11" s="11" t="n">
         <v>2</v>
@@ -5695,19 +5712,19 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>DJI</t>
+          <t>GMB</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Djibouti</t>
+          <t>The Gambia</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="E12" s="11" t="n">
         <v>2</v>
@@ -5716,19 +5733,19 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>MRT</t>
+          <t>MLI</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>Mauritania</t>
+          <t>Mali</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="E13" s="11" t="n">
         <v>2</v>
@@ -5737,12 +5754,12 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>GNQ</t>
+          <t>NER</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Equatorial Guinea</t>
+          <t>Niger</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
@@ -5758,19 +5775,19 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>COG</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>Republic of Congo</t>
+          <t>Democratic Rep. Congo</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E15" s="11" t="n">
         <v>2</v>
@@ -5779,19 +5796,19 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>EGY</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="E16" s="11" t="n">
         <v>2</v>
@@ -5800,43 +5817,43 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>GMB</t>
+          <t>KEN</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>The Gambia</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>TUN</t>
+          <t>LSO</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Lesotho</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -5851,31 +5868,31 @@
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D19" s="11" t="n">
         <v>16</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>MRT</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>Mauritania</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="E20" s="11" t="n">
         <v>1</v>
@@ -5884,19 +5901,19 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>LSO</t>
+          <t>BEN</t>
         </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>Benin</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E21" s="11" t="n">
         <v>1</v>
@@ -5905,19 +5922,19 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>RWA</t>
+          <t>TUN</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E22" s="11" t="n">
         <v>1</v>
@@ -5926,19 +5943,19 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>CIV</t>
+          <t>SEN</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>Cote d'Ivoire</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E23" s="11" t="n">
         <v>1</v>
@@ -5947,19 +5964,19 @@
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>CAF</t>
+          <t>TCD</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>Central African Republic</t>
+          <t>Chad</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="D24" s="11" t="n">
         <v>51</v>
-      </c>
-      <c r="D24" s="11" t="n">
-        <v>52</v>
       </c>
       <c r="E24" s="11" t="n">
         <v>1</v>
@@ -5968,19 +5985,19 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>TCD</t>
+          <t>SDN</t>
         </is>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>Chad</t>
+          <t>Sudan</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E25" s="11" t="n">
         <v>1</v>
@@ -5989,19 +6006,19 @@
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>ERI</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>Eritrea</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="E26" s="11" t="n">
         <v>1</v>
@@ -6010,19 +6027,19 @@
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>MLI</t>
+          <t>LBR</t>
         </is>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>Mali</t>
+          <t>Liberia</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E27" s="11" t="n">
         <v>1</v>
@@ -6031,19 +6048,19 @@
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>NER</t>
+          <t>AGO</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>Niger</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E28" s="11" t="n">
         <v>1</v>
@@ -6052,19 +6069,19 @@
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>NGA</t>
+          <t>GNQ</t>
         </is>
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Equatorial Guinea</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E29" s="11" t="n">
         <v>1</v>
@@ -6073,19 +6090,19 @@
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>COM</t>
+          <t>COG</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>Comoros</t>
+          <t>Republic of Congo</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="E30" s="11" t="n">
         <v>1</v>
@@ -6094,19 +6111,19 @@
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>TGO</t>
+          <t>GAB</t>
         </is>
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>Togo</t>
+          <t>Gabon</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E31" s="11" t="n">
         <v>1</v>
@@ -6115,19 +6132,19 @@
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>STP</t>
+          <t>DJI</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>Sao Tome &amp; Principe</t>
+          <t>Djibouti</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="E32" s="11" t="n">
         <v>1</v>
@@ -6136,19 +6153,19 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>BFA</t>
         </is>
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Burkina Faso</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="E33" s="11" t="n">
         <v>1</v>
@@ -6157,19 +6174,19 @@
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>ZAF</t>
+          <t>SLE</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Sierra Leone</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E34" s="11" t="n">
         <v>1</v>
@@ -6178,64 +6195,64 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>SEN</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>MOZ</t>
+          <t>SYC</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Seychelles</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>SLE</t>
+          <t>MUS</t>
         </is>
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>Sierra Leone</t>
+          <t>Mauritius</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -6262,19 +6279,19 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>NAM</t>
+          <t>DZA</t>
         </is>
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E39" s="11" t="n">
         <v>0</v>
@@ -6304,19 +6321,19 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>BEN</t>
+          <t>CIV</t>
         </is>
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>Benin</t>
+          <t>Cote d'Ivoire</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E41" s="11" t="n">
         <v>0</v>
@@ -6346,12 +6363,12 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>DZA</t>
+          <t>GHA</t>
         </is>
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
@@ -6367,19 +6384,19 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>SYC</t>
+          <t>STP</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>Seychelles</t>
+          <t>Sao Tome &amp; Principe</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="E44" s="11" t="n">
         <v>0</v>
@@ -6388,19 +6405,19 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>MUS</t>
+          <t>RWA</t>
         </is>
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>Mauritius</t>
+          <t>Rwanda</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E45" s="11" t="n">
         <v>0</v>
@@ -6409,19 +6426,19 @@
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>LBR</t>
+          <t>ZAF</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>Liberia</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="E46" s="11" t="n">
         <v>0</v>
@@ -6439,10 +6456,10 @@
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E47" s="11" t="n">
         <v>0</v>
@@ -6460,10 +6477,10 @@
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E48" s="11" t="n">
         <v>0</v>
@@ -6472,19 +6489,19 @@
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>BFA</t>
+          <t>TGO</t>
         </is>
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>Burkina Faso</t>
+          <t>Togo</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E49" s="11" t="n">
         <v>0</v>
@@ -6493,19 +6510,19 @@
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>ZWE</t>
+          <t>MOZ</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E50" s="11" t="n">
         <v>0</v>
@@ -6514,19 +6531,19 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>AGO</t>
+          <t>ZWE</t>
         </is>
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E51" s="11" t="n">
         <v>0</v>
@@ -6535,19 +6552,19 @@
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>SDN</t>
+          <t>NGA</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t>Sudan</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="C52" s="11" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D52" s="11" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E52" s="11" t="n">
         <v>0</v>
@@ -6556,19 +6573,19 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>ERI</t>
+          <t>SOM</t>
         </is>
       </c>
       <c r="B53" s="10" t="inlineStr">
         <is>
-          <t>Eritrea</t>
+          <t>Somalia</t>
         </is>
       </c>
       <c r="C53" s="11" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D53" s="11" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E53" s="11" t="n">
         <v>0</v>
@@ -6577,19 +6594,19 @@
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>SOM</t>
+          <t>CAF</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t>Somalia</t>
+          <t>Central African Republic</t>
         </is>
       </c>
       <c r="C54" s="11" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D54" s="11" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E54" s="11" t="n">
         <v>0</v>
